--- a/input/customers_february.xlsx
+++ b/input/customers_february.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>full_name</t>
   </si>
@@ -28,6 +28,9 @@
     <t>created_at</t>
   </si>
   <si>
+    <t>invoice_amount</t>
+  </si>
+  <si>
     <t>Alice Chen Duplicate</t>
   </si>
   <si>
@@ -59,6 +62,15 @@
   </si>
   <si>
     <t>2026/03/22</t>
+  </si>
+  <si>
+    <t>1,000</t>
+  </si>
+  <si>
+    <t>(1,200.75)</t>
+  </si>
+  <si>
+    <t>4500</t>
   </si>
 </sst>
 </file>
@@ -416,10 +428,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -432,44 +444,56 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
